--- a/Data/pracstheoryCOMPS.xlsx
+++ b/Data/pracstheoryCOMPS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\kjsitfeedback\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357996EA-889E-4246-9D02-2AA04146A8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973856F1-BBF6-41F8-8E81-0FFC6B3712EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Load Distribution25-26 Odd  Sem" sheetId="1" r:id="rId1"/>
@@ -1113,9 +1113,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1124,29 +1142,47 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1157,75 +1193,39 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1493,56 +1493,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="98.25" customHeight="1">
-      <c r="A1" s="125"/>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
+      <c r="A1" s="138"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1">
-      <c r="A2" s="127"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
+      <c r="A2" s="139"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1">
-      <c r="A3" s="129" t="s">
+      <c r="A3" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="130" t="s">
+      <c r="A4" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="130" t="s">
+      <c r="A5" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="131"/>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A6" s="132" t="s">
+      <c r="A6" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="149" t="s">
+      <c r="B6" s="145" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="147" t="s">
@@ -1557,8 +1557,8 @@
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="118"/>
-      <c r="B7" s="150"/>
+      <c r="A7" s="144"/>
+      <c r="B7" s="146"/>
       <c r="C7" s="148"/>
       <c r="D7" s="4"/>
       <c r="E7" s="1" t="s">
@@ -1567,10 +1567,10 @@
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A8" s="122">
+      <c r="A8" s="125">
         <v>1</v>
       </c>
-      <c r="B8" s="139" t="s">
+      <c r="B8" s="114" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1583,8 +1583,8 @@
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A9" s="123"/>
-      <c r="B9" s="139" t="s">
+      <c r="A9" s="127"/>
+      <c r="B9" s="114" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -1599,10 +1599,10 @@
       <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A10" s="122">
+      <c r="A10" s="125">
         <v>2</v>
       </c>
-      <c r="B10" s="139" t="s">
+      <c r="B10" s="114" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="9" t="s">
@@ -1615,8 +1615,8 @@
       <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="139" t="s">
+      <c r="A11" s="127"/>
+      <c r="B11" s="114" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -1631,10 +1631,10 @@
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A12" s="116">
+      <c r="A12" s="122">
         <v>3</v>
       </c>
-      <c r="B12" s="140" t="s">
+      <c r="B12" s="115" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="9" t="s">
@@ -1647,8 +1647,8 @@
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1">
-      <c r="A13" s="152"/>
-      <c r="B13" s="140" t="s">
+      <c r="A13" s="124"/>
+      <c r="B13" s="115" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -1663,10 +1663,10 @@
       <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1">
-      <c r="A14" s="122">
+      <c r="A14" s="125">
         <v>4</v>
       </c>
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="114" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1679,8 +1679,8 @@
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" customHeight="1">
-      <c r="A15" s="123"/>
-      <c r="B15" s="139" t="s">
+      <c r="A15" s="127"/>
+      <c r="B15" s="114" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="65" t="s">
@@ -1695,10 +1695,10 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="21" customHeight="1">
-      <c r="A16" s="122">
+      <c r="A16" s="125">
         <v>5</v>
       </c>
-      <c r="B16" s="139" t="s">
+      <c r="B16" s="114" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="13" t="s">
@@ -1711,8 +1711,8 @@
       <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:6" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="139" t="s">
+      <c r="A17" s="126"/>
+      <c r="B17" s="114" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="13" t="s">
@@ -1727,8 +1727,8 @@
       <c r="F17" s="14"/>
     </row>
     <row r="18" spans="1:6" ht="17.25" customHeight="1">
-      <c r="A18" s="123"/>
-      <c r="B18" s="139" t="s">
+      <c r="A18" s="127"/>
+      <c r="B18" s="114" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="15" t="s">
@@ -1743,10 +1743,10 @@
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A19" s="122">
+      <c r="A19" s="125">
         <v>6</v>
       </c>
-      <c r="B19" s="139" t="s">
+      <c r="B19" s="114" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1759,8 +1759,8 @@
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A20" s="121"/>
-      <c r="B20" s="139" t="s">
+      <c r="A20" s="126"/>
+      <c r="B20" s="114" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -1775,8 +1775,8 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A21" s="123"/>
-      <c r="B21" s="139" t="s">
+      <c r="A21" s="127"/>
+      <c r="B21" s="114" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="15" t="s">
@@ -1791,10 +1791,10 @@
       <c r="F21" s="12"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1">
-      <c r="A22" s="122">
+      <c r="A22" s="125">
         <v>7</v>
       </c>
-      <c r="B22" s="139" t="s">
+      <c r="B22" s="114" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1807,8 +1807,8 @@
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1">
-      <c r="A23" s="121"/>
-      <c r="B23" s="139" t="s">
+      <c r="A23" s="126"/>
+      <c r="B23" s="114" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1821,8 +1821,8 @@
       <c r="F23" s="12"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1">
-      <c r="A24" s="123"/>
-      <c r="B24" s="139" t="s">
+      <c r="A24" s="127"/>
+      <c r="B24" s="114" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="18" t="s">
@@ -1835,10 +1835,10 @@
       <c r="F24" s="96"/>
     </row>
     <row r="25" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A25" s="122">
+      <c r="A25" s="125">
         <v>8</v>
       </c>
-      <c r="B25" s="145" t="s">
+      <c r="B25" s="119" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="20" t="s">
@@ -1851,8 +1851,8 @@
       <c r="F25" s="61"/>
     </row>
     <row r="26" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A26" s="121"/>
-      <c r="B26" s="145" t="s">
+      <c r="A26" s="126"/>
+      <c r="B26" s="119" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="20" t="s">
@@ -1867,8 +1867,8 @@
       <c r="F26" s="60"/>
     </row>
     <row r="27" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A27" s="123"/>
-      <c r="B27" s="145" t="s">
+      <c r="A27" s="127"/>
+      <c r="B27" s="119" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="21" t="s">
@@ -1881,10 +1881,10 @@
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A28" s="122">
+      <c r="A28" s="125">
         <v>9</v>
       </c>
-      <c r="B28" s="139" t="s">
+      <c r="B28" s="114" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="20" t="s">
@@ -1897,8 +1897,8 @@
       <c r="F28" s="50"/>
     </row>
     <row r="29" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A29" s="121"/>
-      <c r="B29" s="139" t="s">
+      <c r="A29" s="126"/>
+      <c r="B29" s="114" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="54" t="s">
@@ -1913,8 +1913,8 @@
       <c r="F29" s="53"/>
     </row>
     <row r="30" spans="1:6" ht="51" customHeight="1">
-      <c r="A30" s="123"/>
-      <c r="B30" s="139" t="s">
+      <c r="A30" s="127"/>
+      <c r="B30" s="114" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="23" t="s">
@@ -1929,10 +1929,10 @@
       <c r="F30" s="62"/>
     </row>
     <row r="31" spans="1:6" ht="42" customHeight="1">
-      <c r="A31" s="122">
+      <c r="A31" s="125">
         <v>10</v>
       </c>
-      <c r="B31" s="139" t="s">
+      <c r="B31" s="114" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="24" t="s">
@@ -1945,8 +1945,8 @@
       <c r="F31" s="51"/>
     </row>
     <row r="32" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A32" s="121"/>
-      <c r="B32" s="139" t="s">
+      <c r="A32" s="126"/>
+      <c r="B32" s="114" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="55" t="s">
@@ -1959,8 +1959,8 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A33" s="123"/>
-      <c r="B33" s="139" t="s">
+      <c r="A33" s="127"/>
+      <c r="B33" s="114" t="s">
         <v>34</v>
       </c>
       <c r="C33" s="21" t="s">
@@ -1973,10 +1973,10 @@
       <c r="F33" s="12"/>
     </row>
     <row r="34" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A34" s="137">
-        <v>11</v>
-      </c>
-      <c r="B34" s="139" t="s">
+      <c r="A34" s="128">
+        <v>11</v>
+      </c>
+      <c r="B34" s="114" t="s">
         <v>38</v>
       </c>
       <c r="C34" s="27" t="s">
@@ -1989,8 +1989,8 @@
       <c r="F34" s="29"/>
     </row>
     <row r="35" spans="1:7" ht="23.25" customHeight="1">
-      <c r="A35" s="119"/>
-      <c r="B35" s="139" t="s">
+      <c r="A35" s="149"/>
+      <c r="B35" s="114" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="30" t="s">
@@ -2003,8 +2003,8 @@
       <c r="F35" s="58"/>
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A36" s="138"/>
-      <c r="B36" s="139" t="s">
+      <c r="A36" s="129"/>
+      <c r="B36" s="114" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="56" t="s">
@@ -2018,10 +2018,10 @@
       <c r="G36" s="112"/>
     </row>
     <row r="37" spans="1:7" ht="35.25" customHeight="1">
-      <c r="A37" s="137">
-        <v>12</v>
-      </c>
-      <c r="B37" s="139" t="s">
+      <c r="A37" s="128">
+        <v>12</v>
+      </c>
+      <c r="B37" s="114" t="s">
         <v>41</v>
       </c>
       <c r="C37" s="32" t="s">
@@ -2034,8 +2034,8 @@
       <c r="F37" s="60"/>
     </row>
     <row r="38" spans="1:7" ht="35.25" customHeight="1">
-      <c r="A38" s="138"/>
-      <c r="B38" s="139" t="s">
+      <c r="A38" s="129"/>
+      <c r="B38" s="114" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="63" t="s">
@@ -2050,10 +2050,10 @@
       <c r="F38" s="60"/>
     </row>
     <row r="39" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A39" s="116">
+      <c r="A39" s="122">
         <v>13</v>
       </c>
-      <c r="B39" s="139" t="s">
+      <c r="B39" s="114" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
@@ -2066,8 +2066,8 @@
       <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A40" s="152"/>
-      <c r="B40" s="139" t="s">
+      <c r="A40" s="124"/>
+      <c r="B40" s="114" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="65" t="s">
@@ -2082,10 +2082,10 @@
       <c r="F40" s="64"/>
     </row>
     <row r="41" spans="1:7" ht="18" customHeight="1">
-      <c r="A41" s="116">
+      <c r="A41" s="122">
         <v>14</v>
       </c>
-      <c r="B41" s="139" t="s">
+      <c r="B41" s="114" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -2098,8 +2098,8 @@
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:7" ht="18" customHeight="1">
-      <c r="A42" s="117"/>
-      <c r="B42" s="139" t="s">
+      <c r="A42" s="123"/>
+      <c r="B42" s="114" t="s">
         <v>44</v>
       </c>
       <c r="C42" s="65" t="s">
@@ -2114,8 +2114,8 @@
       <c r="F42" s="6"/>
     </row>
     <row r="43" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A43" s="152"/>
-      <c r="B43" s="139" t="s">
+      <c r="A43" s="124"/>
+      <c r="B43" s="114" t="s">
         <v>44</v>
       </c>
       <c r="C43" s="25" t="s">
@@ -2128,10 +2128,10 @@
       <c r="F43" s="6"/>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A44" s="116">
+      <c r="A44" s="122">
         <v>15</v>
       </c>
-      <c r="B44" s="139" t="s">
+      <c r="B44" s="114" t="s">
         <v>46</v>
       </c>
       <c r="C44" s="9" t="s">
@@ -2144,8 +2144,8 @@
       <c r="F44" s="6"/>
     </row>
     <row r="45" spans="1:7" ht="15.75">
-      <c r="A45" s="117"/>
-      <c r="B45" s="139" t="s">
+      <c r="A45" s="123"/>
+      <c r="B45" s="114" t="s">
         <v>46</v>
       </c>
       <c r="C45" s="66" t="s">
@@ -2160,8 +2160,8 @@
       <c r="F45" s="6"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A46" s="152"/>
-      <c r="B46" s="139" t="s">
+      <c r="A46" s="124"/>
+      <c r="B46" s="114" t="s">
         <v>46</v>
       </c>
       <c r="C46" s="18" t="s">
@@ -2174,10 +2174,10 @@
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:7" ht="31.5" customHeight="1">
-      <c r="A47" s="116">
+      <c r="A47" s="122">
         <v>16</v>
       </c>
-      <c r="B47" s="139" t="s">
+      <c r="B47" s="114" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="24" t="s">
@@ -2190,8 +2190,8 @@
       <c r="F47" s="6"/>
     </row>
     <row r="48" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A48" s="117"/>
-      <c r="B48" s="139" t="s">
+      <c r="A48" s="123"/>
+      <c r="B48" s="114" t="s">
         <v>49</v>
       </c>
       <c r="C48" s="34" t="s">
@@ -2204,8 +2204,8 @@
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A49" s="152"/>
-      <c r="B49" s="139" t="s">
+      <c r="A49" s="124"/>
+      <c r="B49" s="114" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="67" t="s">
@@ -2220,10 +2220,10 @@
       <c r="F49" s="6"/>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A50" s="116">
+      <c r="A50" s="122">
         <v>17</v>
       </c>
-      <c r="B50" s="139" t="s">
+      <c r="B50" s="114" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="20" t="s">
@@ -2236,8 +2236,8 @@
       <c r="F50" s="6"/>
     </row>
     <row r="51" spans="1:6" ht="33.75" customHeight="1">
-      <c r="A51" s="117"/>
-      <c r="B51" s="139" t="s">
+      <c r="A51" s="123"/>
+      <c r="B51" s="114" t="s">
         <v>51</v>
       </c>
       <c r="C51" s="20" t="s">
@@ -2250,8 +2250,8 @@
       <c r="F51" s="6"/>
     </row>
     <row r="52" spans="1:6" ht="33.75" customHeight="1">
-      <c r="A52" s="152"/>
-      <c r="B52" s="139" t="s">
+      <c r="A52" s="124"/>
+      <c r="B52" s="114" t="s">
         <v>51</v>
       </c>
       <c r="C52" s="54" t="s">
@@ -2266,10 +2266,10 @@
       <c r="F52" s="6"/>
     </row>
     <row r="53" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A53" s="116">
+      <c r="A53" s="122">
         <v>18</v>
       </c>
-      <c r="B53" s="139" t="s">
+      <c r="B53" s="114" t="s">
         <v>54</v>
       </c>
       <c r="C53" s="35" t="s">
@@ -2282,8 +2282,8 @@
       <c r="F53" s="36"/>
     </row>
     <row r="54" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A54" s="117"/>
-      <c r="B54" s="139" t="s">
+      <c r="A54" s="123"/>
+      <c r="B54" s="114" t="s">
         <v>54</v>
       </c>
       <c r="C54" s="68" t="s">
@@ -2296,8 +2296,8 @@
       <c r="F54" s="33"/>
     </row>
     <row r="55" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A55" s="152"/>
-      <c r="B55" s="139" t="s">
+      <c r="A55" s="124"/>
+      <c r="B55" s="114" t="s">
         <v>54</v>
       </c>
       <c r="C55" s="65" t="s">
@@ -2312,10 +2312,10 @@
       <c r="F55" s="6"/>
     </row>
     <row r="56" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A56" s="153">
+      <c r="A56" s="135">
         <v>19</v>
       </c>
-      <c r="B56" s="139" t="s">
+      <c r="B56" s="114" t="s">
         <v>56</v>
       </c>
       <c r="C56" s="9" t="s">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="57" spans="1:6" ht="23.25" customHeight="1">
       <c r="A57" s="136"/>
-      <c r="B57" s="139" t="s">
+      <c r="B57" s="114" t="s">
         <v>56</v>
       </c>
       <c r="C57" s="66" t="s">
@@ -2344,8 +2344,8 @@
       <c r="F57" s="6"/>
     </row>
     <row r="58" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A58" s="154"/>
-      <c r="B58" s="139" t="s">
+      <c r="A58" s="137"/>
+      <c r="B58" s="114" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="90" t="s">
@@ -2360,10 +2360,10 @@
       <c r="F58" s="92"/>
     </row>
     <row r="59" spans="1:6" ht="18" customHeight="1">
-      <c r="A59" s="116">
+      <c r="A59" s="122">
         <v>20</v>
       </c>
-      <c r="B59" s="140" t="s">
+      <c r="B59" s="115" t="s">
         <v>57</v>
       </c>
       <c r="C59" s="37" t="s">
@@ -2376,8 +2376,8 @@
       <c r="F59" s="36"/>
     </row>
     <row r="60" spans="1:6" ht="18" customHeight="1">
-      <c r="A60" s="117"/>
-      <c r="B60" s="140" t="s">
+      <c r="A60" s="123"/>
+      <c r="B60" s="115" t="s">
         <v>57</v>
       </c>
       <c r="C60" s="69" t="s">
@@ -2392,8 +2392,8 @@
       <c r="F60" s="33"/>
     </row>
     <row r="61" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A61" s="152"/>
-      <c r="B61" s="140" t="s">
+      <c r="A61" s="124"/>
+      <c r="B61" s="115" t="s">
         <v>57</v>
       </c>
       <c r="C61" s="70" t="s">
@@ -2408,10 +2408,10 @@
       <c r="F61" s="6"/>
     </row>
     <row r="62" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A62" s="116">
+      <c r="A62" s="122">
         <v>21</v>
       </c>
-      <c r="B62" s="139" t="s">
+      <c r="B62" s="114" t="s">
         <v>59</v>
       </c>
       <c r="C62" s="9" t="s">
@@ -2424,8 +2424,8 @@
       <c r="F62" s="12"/>
     </row>
     <row r="63" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A63" s="117"/>
-      <c r="B63" s="139" t="s">
+      <c r="A63" s="123"/>
+      <c r="B63" s="114" t="s">
         <v>59</v>
       </c>
       <c r="C63" s="66" t="s">
@@ -2440,8 +2440,8 @@
       <c r="F63" s="12"/>
     </row>
     <row r="64" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A64" s="152"/>
-      <c r="B64" s="139" t="s">
+      <c r="A64" s="124"/>
+      <c r="B64" s="114" t="s">
         <v>59</v>
       </c>
       <c r="C64" s="18" t="s">
@@ -2454,10 +2454,10 @@
       <c r="F64" s="12"/>
     </row>
     <row r="65" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A65" s="116">
+      <c r="A65" s="122">
         <v>22</v>
       </c>
-      <c r="B65" s="139" t="s">
+      <c r="B65" s="114" t="s">
         <v>62</v>
       </c>
       <c r="C65" s="9" t="s">
@@ -2470,8 +2470,8 @@
       <c r="F65" s="6"/>
     </row>
     <row r="66" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A66" s="117"/>
-      <c r="B66" s="139" t="s">
+      <c r="A66" s="123"/>
+      <c r="B66" s="114" t="s">
         <v>62</v>
       </c>
       <c r="C66" s="66" t="s">
@@ -2484,8 +2484,8 @@
       <c r="F66" s="6"/>
     </row>
     <row r="67" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A67" s="152"/>
-      <c r="B67" s="139" t="s">
+      <c r="A67" s="124"/>
+      <c r="B67" s="114" t="s">
         <v>62</v>
       </c>
       <c r="C67" s="18" t="s">
@@ -2498,10 +2498,10 @@
       <c r="F67" s="12"/>
     </row>
     <row r="68" spans="1:6" ht="18" customHeight="1">
-      <c r="A68" s="116">
+      <c r="A68" s="122">
         <v>23</v>
       </c>
-      <c r="B68" s="146" t="s">
+      <c r="B68" s="120" t="s">
         <v>64</v>
       </c>
       <c r="C68" s="71" t="s">
@@ -2514,8 +2514,8 @@
       <c r="F68" s="50"/>
     </row>
     <row r="69" spans="1:6" ht="18" customHeight="1">
-      <c r="A69" s="117"/>
-      <c r="B69" s="146" t="s">
+      <c r="A69" s="123"/>
+      <c r="B69" s="120" t="s">
         <v>64</v>
       </c>
       <c r="C69" s="78" t="s">
@@ -2530,8 +2530,8 @@
       <c r="F69" s="53"/>
     </row>
     <row r="70" spans="1:6" ht="18" customHeight="1">
-      <c r="A70" s="117"/>
-      <c r="B70" s="146" t="s">
+      <c r="A70" s="123"/>
+      <c r="B70" s="120" t="s">
         <v>64</v>
       </c>
       <c r="C70" s="74" t="s">
@@ -2544,8 +2544,8 @@
       <c r="F70" s="53"/>
     </row>
     <row r="71" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A71" s="152"/>
-      <c r="B71" s="146" t="s">
+      <c r="A71" s="124"/>
+      <c r="B71" s="120" t="s">
         <v>64</v>
       </c>
       <c r="C71" s="76" t="s">
@@ -2560,10 +2560,10 @@
       <c r="F71" s="77"/>
     </row>
     <row r="72" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A72" s="116">
+      <c r="A72" s="122">
         <v>24</v>
       </c>
-      <c r="B72" s="139" t="s">
+      <c r="B72" s="114" t="s">
         <v>67</v>
       </c>
       <c r="C72" s="73" t="s">
@@ -2576,8 +2576,8 @@
       <c r="F72" s="51"/>
     </row>
     <row r="73" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A73" s="117"/>
-      <c r="B73" s="139" t="s">
+      <c r="A73" s="123"/>
+      <c r="B73" s="114" t="s">
         <v>67</v>
       </c>
       <c r="C73" s="79" t="s">
@@ -2590,8 +2590,8 @@
       <c r="F73" s="51"/>
     </row>
     <row r="74" spans="1:6" ht="18" customHeight="1">
-      <c r="A74" s="152"/>
-      <c r="B74" s="139" t="s">
+      <c r="A74" s="124"/>
+      <c r="B74" s="114" t="s">
         <v>67</v>
       </c>
       <c r="C74" s="18" t="s">
@@ -2720,8 +2720,8 @@
       <c r="F81" s="102"/>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A82" s="133"/>
-      <c r="B82" s="126"/>
+      <c r="A82" s="130"/>
+      <c r="B82" s="131"/>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1">
       <c r="A83" s="42"/>
@@ -2740,21 +2740,21 @@
       <c r="F84" s="7"/>
     </row>
     <row r="85" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A85" s="134" t="s">
+      <c r="A85" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="131"/>
-      <c r="C85" s="131"/>
+      <c r="B85" s="133"/>
+      <c r="C85" s="133"/>
       <c r="D85" s="47"/>
       <c r="E85" s="48"/>
       <c r="F85" s="41"/>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A86" s="135" t="s">
+      <c r="A86" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="B86" s="131"/>
-      <c r="C86" s="131"/>
+      <c r="B86" s="133"/>
+      <c r="C86" s="133"/>
       <c r="D86" s="47"/>
       <c r="E86" s="48"/>
       <c r="F86" s="41"/>
@@ -2762,23 +2762,11 @@
   </sheetData>
   <autoFilter ref="A6:E81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="35">
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:F1"/>
@@ -2789,14 +2777,26 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.28460297884451191" right="0.14230148942225596" top="0.52651551086234716" bottom="0.59600914026227314" header="0" footer="0"/>
@@ -2809,9 +2809,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7FE7005-4C37-4D9B-971D-54A56C9E16FC}">
   <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="121" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2888,7 +2892,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="63">
-      <c r="A8" s="114" t="s">
+      <c r="A8" s="150" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -2899,7 +2903,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="63">
-      <c r="A9" s="115"/>
+      <c r="A9" s="151"/>
       <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
@@ -2908,7 +2912,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="63">
-      <c r="A10" s="124"/>
+      <c r="A10" s="152"/>
       <c r="B10" s="18" t="s">
         <v>27</v>
       </c>
@@ -2917,7 +2921,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="126">
-      <c r="A11" s="142" t="s">
+      <c r="A11" s="116" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="20" t="s">
@@ -2928,7 +2932,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="63">
-      <c r="A12" s="143"/>
+      <c r="A12" s="117"/>
       <c r="B12" s="21" t="s">
         <v>30</v>
       </c>
@@ -2948,7 +2952,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="110.25">
-      <c r="A14" s="114" t="s">
+      <c r="A14" s="150" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -2959,7 +2963,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="63">
-      <c r="A15" s="115"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="55" t="s">
         <v>84</v>
       </c>
@@ -2968,7 +2972,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="78.75">
-      <c r="A16" s="124"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="21" t="s">
         <v>36</v>
       </c>
@@ -2977,7 +2981,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="94.5">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="153" t="s">
         <v>38</v>
       </c>
       <c r="B17" s="27" t="s">
@@ -2988,7 +2992,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="63">
-      <c r="A18" s="120"/>
+      <c r="A18" s="154"/>
       <c r="B18" s="30" t="s">
         <v>40</v>
       </c>
@@ -3059,7 +3063,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="110.25">
-      <c r="A25" s="114" t="s">
+      <c r="A25" s="150" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="24" t="s">
@@ -3070,7 +3074,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="47.25">
-      <c r="A26" s="115"/>
+      <c r="A26" s="151"/>
       <c r="B26" s="34" t="s">
         <v>50</v>
       </c>
@@ -3079,7 +3083,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="94.5">
-      <c r="A27" s="114" t="s">
+      <c r="A27" s="150" t="s">
         <v>51</v>
       </c>
       <c r="B27" s="20" t="s">
@@ -3090,7 +3094,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="157.5">
-      <c r="A28" s="115"/>
+      <c r="A28" s="151"/>
       <c r="B28" s="20" t="s">
         <v>32</v>
       </c>
@@ -3172,7 +3176,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="78.75">
-      <c r="A36" s="144" t="s">
+      <c r="A36" s="118" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="71" t="s">
@@ -3260,9 +3264,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE0CE75-1B91-49D7-9329-B92B242F9E49}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="145" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="147" t="s">
@@ -3276,7 +3286,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="150"/>
+      <c r="A2" s="146"/>
       <c r="B2" s="148"/>
       <c r="C2" s="4"/>
       <c r="D2" s="1" t="s">
@@ -3284,7 +3294,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="63">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="114" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -3298,7 +3308,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="78.75">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="114" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -3312,7 +3322,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="78.75">
-      <c r="A5" s="140" t="s">
+      <c r="A5" s="115" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -3326,7 +3336,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="47.25">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="114" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="65" t="s">
@@ -3340,7 +3350,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="47.25">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="114" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -3354,7 +3364,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="63">
-      <c r="A8" s="139" t="s">
+      <c r="A8" s="114" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -3368,7 +3378,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="63">
-      <c r="A9" s="139" t="s">
+      <c r="A9" s="114" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -3382,7 +3392,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="63">
-      <c r="A10" s="139" t="s">
+      <c r="A10" s="114" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -3396,7 +3406,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="126">
-      <c r="A11" s="145" t="s">
+      <c r="A11" s="119" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="20" t="s">
@@ -3410,7 +3420,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="141.75">
-      <c r="A12" s="139" t="s">
+      <c r="A12" s="114" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="54" t="s">
@@ -3424,7 +3434,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="173.25">
-      <c r="A13" s="139" t="s">
+      <c r="A13" s="114" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="23" t="s">
@@ -3438,7 +3448,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="63">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="114" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="56" t="s">
@@ -3450,7 +3460,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="141.75">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="114" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="63" t="s">
@@ -3464,7 +3474,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="47.25">
-      <c r="A16" s="139" t="s">
+      <c r="A16" s="114" t="s">
         <v>43</v>
       </c>
       <c r="B16" s="65" t="s">
@@ -3478,7 +3488,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="63">
-      <c r="A17" s="139" t="s">
+      <c r="A17" s="114" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="65" t="s">
@@ -3492,7 +3502,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="94.5">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="114" t="s">
         <v>46</v>
       </c>
       <c r="B18" s="66" t="s">
@@ -3506,7 +3516,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="63">
-      <c r="A19" s="139" t="s">
+      <c r="A19" s="114" t="s">
         <v>49</v>
       </c>
       <c r="B19" s="67" t="s">
@@ -3520,7 +3530,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="141.75">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="114" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="54" t="s">
@@ -3534,7 +3544,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="47.25">
-      <c r="A21" s="139" t="s">
+      <c r="A21" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="68" t="s">
@@ -3546,7 +3556,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="63">
-      <c r="A22" s="139" t="s">
+      <c r="A22" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="65" t="s">
@@ -3560,7 +3570,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="63">
-      <c r="A23" s="139" t="s">
+      <c r="A23" s="114" t="s">
         <v>56</v>
       </c>
       <c r="B23" s="66" t="s">
@@ -3574,7 +3584,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="63">
-      <c r="A24" s="139" t="s">
+      <c r="A24" s="114" t="s">
         <v>56</v>
       </c>
       <c r="B24" s="90" t="s">
@@ -3588,7 +3598,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75">
-      <c r="A25" s="140" t="s">
+      <c r="A25" s="115" t="s">
         <v>57</v>
       </c>
       <c r="B25" s="69" t="s">
@@ -3602,7 +3612,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="63">
-      <c r="A26" s="140" t="s">
+      <c r="A26" s="115" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="70" t="s">
@@ -3616,7 +3626,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="110.25">
-      <c r="A27" s="139" t="s">
+      <c r="A27" s="114" t="s">
         <v>59</v>
       </c>
       <c r="B27" s="66" t="s">
@@ -3630,7 +3640,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="110.25">
-      <c r="A28" s="139" t="s">
+      <c r="A28" s="114" t="s">
         <v>62</v>
       </c>
       <c r="B28" s="66" t="s">
@@ -3642,7 +3652,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="94.5">
-      <c r="A29" s="146" t="s">
+      <c r="A29" s="120" t="s">
         <v>64</v>
       </c>
       <c r="B29" s="78" t="s">
@@ -3656,7 +3666,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="63">
-      <c r="A30" s="146" t="s">
+      <c r="A30" s="120" t="s">
         <v>64</v>
       </c>
       <c r="B30" s="76" t="s">
@@ -3670,7 +3680,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="94.5">
-      <c r="A31" s="139" t="s">
+      <c r="A31" s="114" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="79" t="s">
